--- a/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/UNIFICACION/ANDRESM/_SALIDA/reporte_ANDRESM.xlsx
+++ b/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/UNIFICACION/ANDRESM/_SALIDA/reporte_ANDRESM.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/03/2026  11:55</t>
+          <t>Generado: 24/03/2026  14:34</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Pos 3
-Obligaciones Grales y Especificas</t>
+Obligaciones Generales y Especificas</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AE4" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF4" s="11" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="AF5" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AG5" s="10" t="inlineStr">
